--- a/artfynd/A 15112-2026 artfynd.xlsx
+++ b/artfynd/A 15112-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,27 +675,27 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>73982694</v>
+        <v>134348589</v>
       </c>
       <c r="B2" t="n">
-        <v>107376</v>
+        <v>102248</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219955</v>
+        <v>692</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Slåttergubbe</t>
+          <t>Hårginst</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Arnica montana</t>
+          <t>Genista pilosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -703,20 +703,36 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>11 Jussö 450 m OSO, Sm</t>
+          <t>Jussö banvallen östra sidan om järnväg i kanter, Jussö, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>444599</v>
+        <v>444683</v>
       </c>
       <c r="R2" t="n">
-        <v>6351896</v>
+        <v>6351985</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -740,17 +756,27 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>1986-01-01</t>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>20:12</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1990-12-31</t>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>20:12</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 6D0j 4710. SOM: Arnica montana. LEG: Torsten Johansson, Evert Norell</t>
+          <t>Längs järnvägen på östra sidan 7 meter mellan de 2 plantorna</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -759,54 +785,46 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Mark vid jvg-korsning</t>
-        </is>
-      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Margareta Edqvist</t>
+          <t>Isac Dahlström</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Via Margareta Edqvist</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Smålands flora (1978-2007)</t>
-        </is>
-      </c>
+          <t>Isac Dahlström</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>74145467</v>
+        <v>73982694</v>
       </c>
       <c r="B3" t="n">
-        <v>107670</v>
+        <v>107907</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220107</v>
+        <v>219955</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Klofibbla</t>
+          <t>Slåttergubbe</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Crepis tectorum</t>
+          <t>Arnica montana</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -861,7 +879,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 6D0j 4710. SOM: Crepis tectorum. LEG: Torsten Johansson, Evert Norell</t>
+          <t>Smålands flora 2007: KOO: 6D0j 4710. SOM: Arnica montana. LEG: Torsten Johansson, Evert Norell</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -890,6 +908,117 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr">
+        <is>
+          <t>Smålands flora (1978-2007)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>74145467</v>
+      </c>
+      <c r="B4" t="n">
+        <v>108200</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>220107</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Klofibbla</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Crepis tectorum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>11 Jussö 450 m OSO, Sm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>444599</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6351896</v>
+      </c>
+      <c r="S4" t="n">
+        <v>50</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Värnamo</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Värnamo</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>1986-01-01</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>1990-12-31</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Smålands flora 2007: KOO: 6D0j 4710. SOM: Crepis tectorum. LEG: Torsten Johansson, Evert Norell</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Mark vid jvg-korsning</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Margareta Edqvist</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Via Margareta Edqvist</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
         <is>
           <t>Smålands flora (1978-2007)</t>
         </is>

--- a/artfynd/A 15112-2026 artfynd.xlsx
+++ b/artfynd/A 15112-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -801,6 +806,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134348589</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -912,6 +922,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73982694</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1023,8 +1038,18 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74145467</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>